--- a/Instancias Excel/phi_ms.xlsx
+++ b/Instancias Excel/phi_ms.xlsx
@@ -11,10 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t>m</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>nombre</t>
   </si>
@@ -35,7 +32,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -45,10 +42,6 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -96,20 +89,17 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -328,107 +318,89 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="6.0"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
+      <c r="B1" s="1">
+        <v>1.0</v>
       </c>
       <c r="C1" s="1">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D1" s="1">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="E1" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="F1" s="1">
         <v>4.0</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="4">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3">
         <v>1.242</v>
       </c>
-      <c r="D2" s="4">
+      <c r="C2" s="3">
         <v>1.226</v>
       </c>
-      <c r="E2" s="4">
+      <c r="D2" s="3">
         <v>1.161</v>
       </c>
-      <c r="F2" s="4">
+      <c r="E2" s="3">
         <v>1.113</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C3" s="4">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3">
         <v>1.739</v>
       </c>
-      <c r="D3" s="4">
+      <c r="C3" s="3">
         <v>1.716</v>
       </c>
-      <c r="E3" s="4">
+      <c r="D3" s="3">
         <v>1.626</v>
       </c>
-      <c r="F3" s="4">
+      <c r="E3" s="3">
         <v>1.558</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="4">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3">
         <v>4.219</v>
       </c>
-      <c r="D4" s="4">
+      <c r="C4" s="3">
         <v>4.164</v>
       </c>
-      <c r="E4" s="4">
+      <c r="D4" s="3">
         <v>3.945</v>
       </c>
-      <c r="F4" s="4">
+      <c r="E4" s="3">
         <v>3.78</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="4">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3">
         <v>6.944</v>
       </c>
-      <c r="D5" s="4">
+      <c r="C5" s="3">
         <v>6.854</v>
       </c>
-      <c r="E5" s="4">
+      <c r="D5" s="3">
         <v>6.492</v>
       </c>
-      <c r="F5" s="4">
+      <c r="E5" s="3">
         <v>6.221</v>
       </c>
     </row>
